--- a/05 - WorkedHourPointing/01 - LP's/ApontamentoYesica.xlsx
+++ b/05 - WorkedHourPointing/01 - LP's/ApontamentoYesica.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\05 - WorkedHourPointing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\05 - WorkedHourPointing\01 - LP's\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3B8964-6FFF-425D-8A56-046A332F2B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{346E254F-156F-4B90-8DAE-8197508EA83E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{C9D61577-ED6E-49E0-8DF4-9B4D2FEA07AE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="271">
   <si>
     <t>LPs</t>
   </si>
@@ -44,109 +44,811 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP046642</t>
-  </si>
-  <si>
-    <t>LP046644</t>
-  </si>
-  <si>
-    <t>LP046538</t>
-  </si>
-  <si>
-    <t>LP046567</t>
-  </si>
-  <si>
-    <t>LP046537</t>
-  </si>
-  <si>
-    <t>LP046682</t>
-  </si>
-  <si>
-    <t>LP047226</t>
-  </si>
-  <si>
-    <t>LP046627</t>
-  </si>
-  <si>
-    <t>LP046620</t>
-  </si>
-  <si>
-    <t>LP047343</t>
-  </si>
-  <si>
-    <t>LP046889</t>
-  </si>
-  <si>
-    <t>LP046890</t>
-  </si>
-  <si>
-    <t>LP047396</t>
-  </si>
-  <si>
-    <t>LP046976</t>
-  </si>
-  <si>
-    <t>LP047400</t>
-  </si>
-  <si>
-    <t>LP046999</t>
-  </si>
-  <si>
-    <t>LP047448</t>
-  </si>
-  <si>
-    <t>LP047406</t>
-  </si>
-  <si>
-    <t>LP047975</t>
-  </si>
-  <si>
-    <t>LP047661</t>
-  </si>
-  <si>
-    <t>LP047654</t>
-  </si>
-  <si>
-    <t>LP047662</t>
-  </si>
-  <si>
-    <t>LP047697</t>
-  </si>
-  <si>
-    <t>LP047698</t>
-  </si>
-  <si>
-    <t>LP047664</t>
-  </si>
-  <si>
-    <t>LP047723</t>
-  </si>
-  <si>
-    <t>LP047733</t>
-  </si>
-  <si>
-    <t>LP047730</t>
-  </si>
-  <si>
-    <t>LP047727</t>
-  </si>
-  <si>
-    <t>LP047728</t>
-  </si>
-  <si>
-    <t>LP047978</t>
-  </si>
-  <si>
-    <t>LP048050</t>
-  </si>
-  <si>
-    <t>LP048185</t>
-  </si>
-  <si>
-    <t>LP048186</t>
-  </si>
-  <si>
-    <t>LP047956</t>
+    <t>LP051411</t>
+  </si>
+  <si>
+    <t>LP051359</t>
+  </si>
+  <si>
+    <t>LP051177</t>
+  </si>
+  <si>
+    <t>LP051176</t>
+  </si>
+  <si>
+    <t>LP051147</t>
+  </si>
+  <si>
+    <t>LP051146</t>
+  </si>
+  <si>
+    <t>LP050630</t>
+  </si>
+  <si>
+    <t>LP050621</t>
+  </si>
+  <si>
+    <t>LP050619</t>
+  </si>
+  <si>
+    <t>LP050618</t>
+  </si>
+  <si>
+    <t>LP050593</t>
+  </si>
+  <si>
+    <t>LP050580</t>
+  </si>
+  <si>
+    <t>LP050574</t>
+  </si>
+  <si>
+    <t>LP050572</t>
+  </si>
+  <si>
+    <t>LP050565</t>
+  </si>
+  <si>
+    <t>LP050554</t>
+  </si>
+  <si>
+    <t>LP050541</t>
+  </si>
+  <si>
+    <t>LP050538</t>
+  </si>
+  <si>
+    <t>LP050530</t>
+  </si>
+  <si>
+    <t>LP050505</t>
+  </si>
+  <si>
+    <t>LP050502</t>
+  </si>
+  <si>
+    <t>LP050501</t>
+  </si>
+  <si>
+    <t>LP050500</t>
+  </si>
+  <si>
+    <t>LP050499</t>
+  </si>
+  <si>
+    <t>LP050498</t>
+  </si>
+  <si>
+    <t>LP050497</t>
+  </si>
+  <si>
+    <t>LP050496</t>
+  </si>
+  <si>
+    <t>LP050487</t>
+  </si>
+  <si>
+    <t>LP050486</t>
+  </si>
+  <si>
+    <t>LP050485</t>
+  </si>
+  <si>
+    <t>LP050484</t>
+  </si>
+  <si>
+    <t>LP050483</t>
+  </si>
+  <si>
+    <t>LP050480</t>
+  </si>
+  <si>
+    <t>LP050440</t>
+  </si>
+  <si>
+    <t>LP050374</t>
+  </si>
+  <si>
+    <t>LP050372</t>
+  </si>
+  <si>
+    <t>LP050367</t>
+  </si>
+  <si>
+    <t>LP050296</t>
+  </si>
+  <si>
+    <t>LP050263</t>
+  </si>
+  <si>
+    <t>LP050151</t>
+  </si>
+  <si>
+    <t>LP050150</t>
+  </si>
+  <si>
+    <t>LP050077</t>
+  </si>
+  <si>
+    <t>LP050007</t>
+  </si>
+  <si>
+    <t>LP050005</t>
+  </si>
+  <si>
+    <t>LP050001</t>
+  </si>
+  <si>
+    <t>LP049891</t>
+  </si>
+  <si>
+    <t>LP049890</t>
+  </si>
+  <si>
+    <t>LP049889</t>
+  </si>
+  <si>
+    <t>LP049869</t>
+  </si>
+  <si>
+    <t>LP049836</t>
+  </si>
+  <si>
+    <t>LP049826</t>
+  </si>
+  <si>
+    <t>LP049808</t>
+  </si>
+  <si>
+    <t>LP049802</t>
+  </si>
+  <si>
+    <t>LP049780</t>
+  </si>
+  <si>
+    <t>LP049720</t>
+  </si>
+  <si>
+    <t>LP049701</t>
+  </si>
+  <si>
+    <t>LP051764</t>
+  </si>
+  <si>
+    <t>LP051524</t>
+  </si>
+  <si>
+    <t>LP051429</t>
+  </si>
+  <si>
+    <t>LP051274</t>
+  </si>
+  <si>
+    <t>LP051272</t>
+  </si>
+  <si>
+    <t>LP051270</t>
+  </si>
+  <si>
+    <t>LP051269</t>
+  </si>
+  <si>
+    <t>LP051263</t>
+  </si>
+  <si>
+    <t>LP051252</t>
+  </si>
+  <si>
+    <t>LP051236</t>
+  </si>
+  <si>
+    <t>LP051234</t>
+  </si>
+  <si>
+    <t>LP051233</t>
+  </si>
+  <si>
+    <t>LP051228</t>
+  </si>
+  <si>
+    <t>LP051191</t>
+  </si>
+  <si>
+    <t>LP051165</t>
+  </si>
+  <si>
+    <t>LP051163</t>
+  </si>
+  <si>
+    <t>LP051143</t>
+  </si>
+  <si>
+    <t>LP051136</t>
+  </si>
+  <si>
+    <t>LP051128</t>
+  </si>
+  <si>
+    <t>LP051127</t>
+  </si>
+  <si>
+    <t>LP051126</t>
+  </si>
+  <si>
+    <t>LP051125</t>
+  </si>
+  <si>
+    <t>LP051120</t>
+  </si>
+  <si>
+    <t>LP051119</t>
+  </si>
+  <si>
+    <t>LP051113</t>
+  </si>
+  <si>
+    <t>LP051112</t>
+  </si>
+  <si>
+    <t>LP051111</t>
+  </si>
+  <si>
+    <t>LP051109</t>
+  </si>
+  <si>
+    <t>LP051108</t>
+  </si>
+  <si>
+    <t>LP051107</t>
+  </si>
+  <si>
+    <t>LP051101</t>
+  </si>
+  <si>
+    <t>LP051100</t>
+  </si>
+  <si>
+    <t>LP051094</t>
+  </si>
+  <si>
+    <t>LP051093</t>
+  </si>
+  <si>
+    <t>LP051090</t>
+  </si>
+  <si>
+    <t>LP051015</t>
+  </si>
+  <si>
+    <t>LP051014</t>
+  </si>
+  <si>
+    <t>LP051012</t>
+  </si>
+  <si>
+    <t>LP051011</t>
+  </si>
+  <si>
+    <t>LP051006</t>
+  </si>
+  <si>
+    <t>LP050988</t>
+  </si>
+  <si>
+    <t>LP050987</t>
+  </si>
+  <si>
+    <t>LP050986</t>
+  </si>
+  <si>
+    <t>LP050983</t>
+  </si>
+  <si>
+    <t>LP050982</t>
+  </si>
+  <si>
+    <t>LP050962</t>
+  </si>
+  <si>
+    <t>LP050961</t>
+  </si>
+  <si>
+    <t>LP050960</t>
+  </si>
+  <si>
+    <t>LP050958</t>
+  </si>
+  <si>
+    <t>LP050956</t>
+  </si>
+  <si>
+    <t>LP050939</t>
+  </si>
+  <si>
+    <t>LP050929</t>
+  </si>
+  <si>
+    <t>LP050925</t>
+  </si>
+  <si>
+    <t>LP050914</t>
+  </si>
+  <si>
+    <t>LP050898</t>
+  </si>
+  <si>
+    <t>LP050879</t>
+  </si>
+  <si>
+    <t>LP050878</t>
+  </si>
+  <si>
+    <t>LP050873</t>
+  </si>
+  <si>
+    <t>LP050862</t>
+  </si>
+  <si>
+    <t>LP050860</t>
+  </si>
+  <si>
+    <t>LP050859</t>
+  </si>
+  <si>
+    <t>LP050858</t>
+  </si>
+  <si>
+    <t>LP050852</t>
+  </si>
+  <si>
+    <t>LP050851</t>
+  </si>
+  <si>
+    <t>LP050844</t>
+  </si>
+  <si>
+    <t>LP050842</t>
+  </si>
+  <si>
+    <t>LP050838</t>
+  </si>
+  <si>
+    <t>LP050831</t>
+  </si>
+  <si>
+    <t>LP050827</t>
+  </si>
+  <si>
+    <t>LP050826</t>
+  </si>
+  <si>
+    <t>LP050825</t>
+  </si>
+  <si>
+    <t>LP050795</t>
+  </si>
+  <si>
+    <t>LP050708</t>
+  </si>
+  <si>
+    <t>LP050701</t>
+  </si>
+  <si>
+    <t>LP050699</t>
+  </si>
+  <si>
+    <t>LP050698</t>
+  </si>
+  <si>
+    <t>LP050697</t>
+  </si>
+  <si>
+    <t>LP050696</t>
+  </si>
+  <si>
+    <t>LP050695</t>
+  </si>
+  <si>
+    <t>LP050694</t>
+  </si>
+  <si>
+    <t>LP050693</t>
+  </si>
+  <si>
+    <t>LP050692</t>
+  </si>
+  <si>
+    <t>LP050691</t>
+  </si>
+  <si>
+    <t>LP050636</t>
+  </si>
+  <si>
+    <t>LP050635</t>
+  </si>
+  <si>
+    <t>LP050633</t>
+  </si>
+  <si>
+    <t>LP050631</t>
+  </si>
+  <si>
+    <t>LP050610</t>
+  </si>
+  <si>
+    <t>LP050608</t>
+  </si>
+  <si>
+    <t>LP050607</t>
+  </si>
+  <si>
+    <t>LP052462</t>
+  </si>
+  <si>
+    <t>LP052204</t>
+  </si>
+  <si>
+    <t>LP052153</t>
+  </si>
+  <si>
+    <t>LP052135</t>
+  </si>
+  <si>
+    <t>LP052077</t>
+  </si>
+  <si>
+    <t>LP052076</t>
+  </si>
+  <si>
+    <t>LP052075</t>
+  </si>
+  <si>
+    <t>LP052059</t>
+  </si>
+  <si>
+    <t>LP052018</t>
+  </si>
+  <si>
+    <t>LP052017</t>
+  </si>
+  <si>
+    <t>LP052016</t>
+  </si>
+  <si>
+    <t>LP052011</t>
+  </si>
+  <si>
+    <t>LP052009</t>
+  </si>
+  <si>
+    <t>LP052008</t>
+  </si>
+  <si>
+    <t>LP051999</t>
+  </si>
+  <si>
+    <t>LP051998</t>
+  </si>
+  <si>
+    <t>LP051997</t>
+  </si>
+  <si>
+    <t>LP051996</t>
+  </si>
+  <si>
+    <t>LP051995</t>
+  </si>
+  <si>
+    <t>LP051994</t>
+  </si>
+  <si>
+    <t>LP051993</t>
+  </si>
+  <si>
+    <t>LP051991</t>
+  </si>
+  <si>
+    <t>LP051990</t>
+  </si>
+  <si>
+    <t>LP051986</t>
+  </si>
+  <si>
+    <t>LP051985</t>
+  </si>
+  <si>
+    <t>LP051966</t>
+  </si>
+  <si>
+    <t>LP051962</t>
+  </si>
+  <si>
+    <t>LP051930</t>
+  </si>
+  <si>
+    <t>LP051927</t>
+  </si>
+  <si>
+    <t>LP051910</t>
+  </si>
+  <si>
+    <t>LP051909</t>
+  </si>
+  <si>
+    <t>LP051908</t>
+  </si>
+  <si>
+    <t>LP051907</t>
+  </si>
+  <si>
+    <t>LP051906</t>
+  </si>
+  <si>
+    <t>LP051905</t>
+  </si>
+  <si>
+    <t>LP051904</t>
+  </si>
+  <si>
+    <t>LP051903</t>
+  </si>
+  <si>
+    <t>LP051902</t>
+  </si>
+  <si>
+    <t>LP051901</t>
+  </si>
+  <si>
+    <t>LP051895</t>
+  </si>
+  <si>
+    <t>LP051887</t>
+  </si>
+  <si>
+    <t>LP051886</t>
+  </si>
+  <si>
+    <t>LP051885</t>
+  </si>
+  <si>
+    <t>LP051884</t>
+  </si>
+  <si>
+    <t>LP051883</t>
+  </si>
+  <si>
+    <t>LP051867</t>
+  </si>
+  <si>
+    <t>LP051866</t>
+  </si>
+  <si>
+    <t>LP051865</t>
+  </si>
+  <si>
+    <t>LP051864</t>
+  </si>
+  <si>
+    <t>LP051863</t>
+  </si>
+  <si>
+    <t>LP051859</t>
+  </si>
+  <si>
+    <t>LP051853</t>
+  </si>
+  <si>
+    <t>LP051851</t>
+  </si>
+  <si>
+    <t>LP051849</t>
+  </si>
+  <si>
+    <t>LP051848</t>
+  </si>
+  <si>
+    <t>LP051847</t>
+  </si>
+  <si>
+    <t>LP051846</t>
+  </si>
+  <si>
+    <t>LP051845</t>
+  </si>
+  <si>
+    <t>LP051757</t>
+  </si>
+  <si>
+    <t>LP051756</t>
+  </si>
+  <si>
+    <t>LP051755</t>
+  </si>
+  <si>
+    <t>LP051754</t>
+  </si>
+  <si>
+    <t>LP051753</t>
+  </si>
+  <si>
+    <t>LP051752</t>
+  </si>
+  <si>
+    <t>LP051751</t>
+  </si>
+  <si>
+    <t>LP051750</t>
+  </si>
+  <si>
+    <t>LP051749</t>
+  </si>
+  <si>
+    <t>LP051746</t>
+  </si>
+  <si>
+    <t>LP051745</t>
+  </si>
+  <si>
+    <t>LP051736</t>
+  </si>
+  <si>
+    <t>LP051709</t>
+  </si>
+  <si>
+    <t>LP051687</t>
+  </si>
+  <si>
+    <t>LP051686</t>
+  </si>
+  <si>
+    <t>LP051685</t>
+  </si>
+  <si>
+    <t>LP051684</t>
+  </si>
+  <si>
+    <t>LP051683</t>
+  </si>
+  <si>
+    <t>LP051682</t>
+  </si>
+  <si>
+    <t>LP051680</t>
+  </si>
+  <si>
+    <t>LP051665</t>
+  </si>
+  <si>
+    <t>LP051664</t>
+  </si>
+  <si>
+    <t>LP051661</t>
+  </si>
+  <si>
+    <t>LP051659</t>
+  </si>
+  <si>
+    <t>LP051658</t>
+  </si>
+  <si>
+    <t>LP051657</t>
+  </si>
+  <si>
+    <t>LP051656</t>
+  </si>
+  <si>
+    <t>LP051629</t>
+  </si>
+  <si>
+    <t>LP051627</t>
+  </si>
+  <si>
+    <t>LP051626</t>
+  </si>
+  <si>
+    <t>LP051618</t>
+  </si>
+  <si>
+    <t>LP051617</t>
+  </si>
+  <si>
+    <t>LP051609</t>
+  </si>
+  <si>
+    <t>LP051608</t>
+  </si>
+  <si>
+    <t>LP051607</t>
+  </si>
+  <si>
+    <t>LP051606</t>
+  </si>
+  <si>
+    <t>LP051605</t>
+  </si>
+  <si>
+    <t>LP051604</t>
+  </si>
+  <si>
+    <t>LP051603</t>
+  </si>
+  <si>
+    <t>LP051602</t>
+  </si>
+  <si>
+    <t>LP051601</t>
+  </si>
+  <si>
+    <t>LP051600</t>
+  </si>
+  <si>
+    <t>LP051599</t>
+  </si>
+  <si>
+    <t>LP051598</t>
+  </si>
+  <si>
+    <t>LP051575</t>
+  </si>
+  <si>
+    <t>LP051570</t>
+  </si>
+  <si>
+    <t>LP051537</t>
+  </si>
+  <si>
+    <t>LP051507</t>
+  </si>
+  <si>
+    <t>LP051506</t>
+  </si>
+  <si>
+    <t>LP051504</t>
+  </si>
+  <si>
+    <t>LP051502</t>
+  </si>
+  <si>
+    <t>LP051501</t>
+  </si>
+  <si>
+    <t>LP051500</t>
+  </si>
+  <si>
+    <t>LP051498</t>
+  </si>
+  <si>
+    <t>LP051497</t>
+  </si>
+  <si>
+    <t>LP051496</t>
+  </si>
+  <si>
+    <t>LP051495</t>
+  </si>
+  <si>
+    <t>LP051494</t>
+  </si>
+  <si>
+    <t>LP051409</t>
+  </si>
+  <si>
+    <t>LP051404</t>
+  </si>
+  <si>
+    <t>LP051403</t>
+  </si>
+  <si>
+    <t>LP051375</t>
+  </si>
+  <si>
+    <t>LP051320</t>
+  </si>
+  <si>
+    <t>31.10.2025</t>
+  </si>
+  <si>
+    <t>30.10.2025</t>
   </si>
 </sst>
 </file>
@@ -214,7 +916,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -531,193 +1233,1068 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B67CD9C8-C549-42C7-8116-4422AAB55D3F}">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>270</v>
+      </c>
+      <c r="H1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>73</v>
+      </c>
+      <c r="H17" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E18" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E19" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E20" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E23" t="s">
+        <v>79</v>
+      </c>
+      <c r="H23" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
+        <v>80</v>
+      </c>
+      <c r="H24" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E25" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E26" t="s">
+        <v>82</v>
+      </c>
+      <c r="H26" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E27" t="s">
+        <v>83</v>
+      </c>
+      <c r="H27" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E28" t="s">
+        <v>84</v>
+      </c>
+      <c r="H28" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E29" t="s">
+        <v>85</v>
+      </c>
+      <c r="H29" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E30" t="s">
+        <v>86</v>
+      </c>
+      <c r="H30" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E31" t="s">
+        <v>87</v>
+      </c>
+      <c r="H31" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E32" t="s">
+        <v>88</v>
+      </c>
+      <c r="H32" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E33" t="s">
+        <v>89</v>
+      </c>
+      <c r="H33" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H34" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H35" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>36</v>
+      </c>
+      <c r="E36" t="s">
+        <v>92</v>
+      </c>
+      <c r="H36" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="E37" t="s">
+        <v>93</v>
+      </c>
+      <c r="H37" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" t="s">
+        <v>94</v>
+      </c>
+      <c r="H38" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39" t="s">
+        <v>95</v>
+      </c>
+      <c r="H39" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" t="s">
+        <v>96</v>
+      </c>
+      <c r="H40" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+      <c r="E41" t="s">
+        <v>97</v>
+      </c>
+      <c r="H41" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+      <c r="E42" t="s">
+        <v>98</v>
+      </c>
+      <c r="H42" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E43" t="s">
+        <v>99</v>
+      </c>
+      <c r="H43" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="E44" t="s">
+        <v>100</v>
+      </c>
+      <c r="H44" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+      <c r="E45" t="s">
+        <v>101</v>
+      </c>
+      <c r="H45" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+      <c r="E46" t="s">
+        <v>102</v>
+      </c>
+      <c r="H46" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+      <c r="E47" t="s">
+        <v>103</v>
+      </c>
+      <c r="H47" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+      <c r="E48" t="s">
+        <v>104</v>
+      </c>
+      <c r="H48" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+      <c r="E49" t="s">
+        <v>105</v>
+      </c>
+      <c r="H49" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+      <c r="E50" t="s">
+        <v>106</v>
+      </c>
+      <c r="H50" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+      <c r="E51" t="s">
+        <v>107</v>
+      </c>
+      <c r="H51" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+      <c r="E52" t="s">
+        <v>108</v>
+      </c>
+      <c r="H52" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+      <c r="E53" t="s">
+        <v>109</v>
+      </c>
+      <c r="H53" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+      <c r="E54" t="s">
+        <v>110</v>
+      </c>
+      <c r="H54" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E55" t="s">
+        <v>111</v>
+      </c>
+      <c r="H55" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+      <c r="E56" t="s">
+        <v>112</v>
+      </c>
+      <c r="H56" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+      <c r="E57" t="s">
+        <v>113</v>
+      </c>
+      <c r="H57" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E58" t="s">
+        <v>114</v>
+      </c>
+      <c r="H58" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E59" t="s">
+        <v>115</v>
+      </c>
+      <c r="H59" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E60" t="s">
+        <v>116</v>
+      </c>
+      <c r="H60" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E61" t="s">
+        <v>117</v>
+      </c>
+      <c r="H61" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E62" t="s">
+        <v>118</v>
+      </c>
+      <c r="H62" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E63" t="s">
+        <v>119</v>
+      </c>
+      <c r="H63" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E64" t="s">
+        <v>120</v>
+      </c>
+      <c r="H64" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="65" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E65" t="s">
+        <v>121</v>
+      </c>
+      <c r="H65" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="66" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E66" t="s">
+        <v>122</v>
+      </c>
+      <c r="H66" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="67" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E67" t="s">
+        <v>123</v>
+      </c>
+      <c r="H67" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="68" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E68" t="s">
+        <v>124</v>
+      </c>
+      <c r="H68" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="69" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E69" t="s">
+        <v>125</v>
+      </c>
+      <c r="H69" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="70" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E70" t="s">
+        <v>126</v>
+      </c>
+      <c r="H70" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="71" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E71" t="s">
+        <v>127</v>
+      </c>
+      <c r="H71" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="72" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E72" t="s">
+        <v>128</v>
+      </c>
+      <c r="H72" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="73" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E73" t="s">
+        <v>129</v>
+      </c>
+      <c r="H73" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="74" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E74" t="s">
+        <v>130</v>
+      </c>
+      <c r="H74" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="75" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E75" t="s">
+        <v>131</v>
+      </c>
+      <c r="H75" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="76" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E76" t="s">
+        <v>132</v>
+      </c>
+      <c r="H76" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="77" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E77" t="s">
+        <v>133</v>
+      </c>
+      <c r="H77" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="78" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E78" t="s">
+        <v>134</v>
+      </c>
+      <c r="H78" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="79" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E79" t="s">
+        <v>135</v>
+      </c>
+      <c r="H79" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="80" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E80" t="s">
+        <v>136</v>
+      </c>
+      <c r="H80" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="81" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E81" t="s">
+        <v>137</v>
+      </c>
+      <c r="H81" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="82" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E82" t="s">
+        <v>138</v>
+      </c>
+      <c r="H82" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="83" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E83" t="s">
+        <v>139</v>
+      </c>
+      <c r="H83" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="84" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E84" t="s">
+        <v>140</v>
+      </c>
+      <c r="H84" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="85" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E85" t="s">
+        <v>141</v>
+      </c>
+      <c r="H85" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="86" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E86" t="s">
+        <v>142</v>
+      </c>
+      <c r="H86" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="87" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E87" t="s">
+        <v>143</v>
+      </c>
+      <c r="H87" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="88" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E88" t="s">
+        <v>144</v>
+      </c>
+      <c r="H88" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="89" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E89" t="s">
+        <v>145</v>
+      </c>
+      <c r="H89" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="90" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E90" t="s">
+        <v>146</v>
+      </c>
+      <c r="H90" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="91" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E91" t="s">
+        <v>147</v>
+      </c>
+      <c r="H91" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="92" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="H92" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="93" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="H93" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="94" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="H94" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="95" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="H95" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="96" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="H96" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="97" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H97" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="98" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H98" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="99" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H99" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="100" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H100" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="101" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H101" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="102" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H102" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="103" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H103" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="104" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H104" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="105" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H105" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="106" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H106" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="107" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H107" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="108" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H108" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="109" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H109" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="110" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H110" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="111" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H111" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="112" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H112" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="113" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H113" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="114" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H114" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="115" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H115" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="116" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H116" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="117" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H117" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="118" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H118" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="119" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H119" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="120" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H120" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="121" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H121" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="122" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H122" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/05 - WorkedHourPointing/01 - LP's/ApontamentoYesica.xlsx
+++ b/05 - WorkedHourPointing/01 - LP's/ApontamentoYesica.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\05 - WorkedHourPointing\01 - LP's\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42746349-4608-448B-9B9B-8ED03BF91D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB999DD2-C82A-4D96-B779-79CFC743DDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="1095" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
   <si>
     <t>LPs</t>
   </si>
@@ -28,544 +28,271 @@
     <t>Status</t>
   </si>
   <si>
-    <t>31.10.2025</t>
-  </si>
-  <si>
-    <t>LP051764</t>
-  </si>
-  <si>
     <t>LP052462</t>
   </si>
   <si>
-    <t>LP051524</t>
-  </si>
-  <si>
     <t>LP052204</t>
   </si>
   <si>
-    <t>LP051429</t>
-  </si>
-  <si>
     <t>LP052153</t>
   </si>
   <si>
-    <t>LP051274</t>
-  </si>
-  <si>
     <t>LP052135</t>
   </si>
   <si>
-    <t>LP051272</t>
-  </si>
-  <si>
     <t>LP052077</t>
   </si>
   <si>
-    <t>LP051270</t>
-  </si>
-  <si>
     <t>LP052076</t>
   </si>
   <si>
-    <t>LP051269</t>
-  </si>
-  <si>
     <t>LP052075</t>
   </si>
   <si>
-    <t>LP051263</t>
-  </si>
-  <si>
     <t>LP052059</t>
   </si>
   <si>
-    <t>LP051252</t>
-  </si>
-  <si>
     <t>LP052018</t>
   </si>
   <si>
-    <t>LP051236</t>
-  </si>
-  <si>
     <t>LP052017</t>
   </si>
   <si>
-    <t>LP051234</t>
-  </si>
-  <si>
     <t>LP052016</t>
   </si>
   <si>
-    <t>LP051233</t>
-  </si>
-  <si>
     <t>LP052011</t>
   </si>
   <si>
-    <t>LP051228</t>
-  </si>
-  <si>
     <t>LP052009</t>
   </si>
   <si>
-    <t>LP051191</t>
-  </si>
-  <si>
     <t>LP052008</t>
   </si>
   <si>
-    <t>LP051165</t>
-  </si>
-  <si>
     <t>LP051999</t>
   </si>
   <si>
-    <t>LP051163</t>
-  </si>
-  <si>
     <t>LP051998</t>
   </si>
   <si>
-    <t>LP051143</t>
-  </si>
-  <si>
     <t>LP051997</t>
   </si>
   <si>
-    <t>LP051136</t>
-  </si>
-  <si>
     <t>LP051996</t>
   </si>
   <si>
-    <t>LP051128</t>
-  </si>
-  <si>
     <t>LP051995</t>
   </si>
   <si>
-    <t>LP051127</t>
-  </si>
-  <si>
     <t>LP051994</t>
   </si>
   <si>
-    <t>LP051126</t>
-  </si>
-  <si>
     <t>LP051993</t>
   </si>
   <si>
-    <t>LP051125</t>
-  </si>
-  <si>
     <t>LP051991</t>
   </si>
   <si>
-    <t>LP051120</t>
-  </si>
-  <si>
     <t>LP051990</t>
   </si>
   <si>
-    <t>LP051119</t>
-  </si>
-  <si>
     <t>LP051986</t>
   </si>
   <si>
-    <t>LP051113</t>
-  </si>
-  <si>
     <t>LP051985</t>
   </si>
   <si>
-    <t>LP051112</t>
-  </si>
-  <si>
     <t>LP051966</t>
   </si>
   <si>
-    <t>LP051111</t>
-  </si>
-  <si>
     <t>LP051962</t>
   </si>
   <si>
-    <t>LP051109</t>
-  </si>
-  <si>
     <t>LP051930</t>
   </si>
   <si>
-    <t>LP051108</t>
-  </si>
-  <si>
     <t>LP051927</t>
   </si>
   <si>
-    <t>LP051107</t>
-  </si>
-  <si>
     <t>LP051910</t>
   </si>
   <si>
-    <t>LP051101</t>
-  </si>
-  <si>
     <t>LP051909</t>
   </si>
   <si>
-    <t>LP051100</t>
-  </si>
-  <si>
     <t>LP051908</t>
   </si>
   <si>
-    <t>LP051094</t>
-  </si>
-  <si>
     <t>LP051907</t>
   </si>
   <si>
-    <t>LP051093</t>
-  </si>
-  <si>
     <t>LP051906</t>
   </si>
   <si>
-    <t>LP051090</t>
-  </si>
-  <si>
     <t>LP051905</t>
   </si>
   <si>
-    <t>LP051015</t>
-  </si>
-  <si>
     <t>LP051904</t>
   </si>
   <si>
-    <t>LP051014</t>
-  </si>
-  <si>
     <t>LP051903</t>
   </si>
   <si>
-    <t>LP051012</t>
-  </si>
-  <si>
     <t>LP051902</t>
   </si>
   <si>
-    <t>LP051011</t>
-  </si>
-  <si>
     <t>LP051901</t>
   </si>
   <si>
-    <t>LP051006</t>
-  </si>
-  <si>
     <t>LP051895</t>
   </si>
   <si>
-    <t>LP050988</t>
-  </si>
-  <si>
     <t>LP051887</t>
   </si>
   <si>
-    <t>LP050987</t>
-  </si>
-  <si>
     <t>LP051886</t>
   </si>
   <si>
-    <t>LP050986</t>
-  </si>
-  <si>
     <t>LP051885</t>
   </si>
   <si>
-    <t>LP050983</t>
-  </si>
-  <si>
     <t>LP051884</t>
   </si>
   <si>
-    <t>LP050982</t>
-  </si>
-  <si>
     <t>LP051883</t>
   </si>
   <si>
-    <t>LP050962</t>
-  </si>
-  <si>
     <t>LP051867</t>
   </si>
   <si>
-    <t>LP050961</t>
-  </si>
-  <si>
     <t>LP051866</t>
   </si>
   <si>
-    <t>LP050960</t>
-  </si>
-  <si>
     <t>LP051865</t>
   </si>
   <si>
-    <t>LP050958</t>
-  </si>
-  <si>
     <t>LP051864</t>
   </si>
   <si>
-    <t>LP050956</t>
-  </si>
-  <si>
     <t>LP051863</t>
   </si>
   <si>
-    <t>LP050939</t>
-  </si>
-  <si>
     <t>LP051859</t>
   </si>
   <si>
-    <t>LP050929</t>
-  </si>
-  <si>
     <t>LP051853</t>
   </si>
   <si>
-    <t>LP050925</t>
-  </si>
-  <si>
     <t>LP051851</t>
   </si>
   <si>
-    <t>LP050914</t>
-  </si>
-  <si>
     <t>LP051849</t>
   </si>
   <si>
-    <t>LP050898</t>
-  </si>
-  <si>
     <t>LP051848</t>
   </si>
   <si>
-    <t>LP050879</t>
-  </si>
-  <si>
     <t>LP051847</t>
   </si>
   <si>
-    <t>LP050878</t>
-  </si>
-  <si>
     <t>LP051846</t>
   </si>
   <si>
-    <t>LP050873</t>
-  </si>
-  <si>
     <t>LP051845</t>
   </si>
   <si>
-    <t>LP050862</t>
-  </si>
-  <si>
     <t>LP051757</t>
   </si>
   <si>
-    <t>LP050860</t>
-  </si>
-  <si>
     <t>LP051756</t>
   </si>
   <si>
-    <t>LP050859</t>
-  </si>
-  <si>
     <t>LP051755</t>
   </si>
   <si>
-    <t>LP050858</t>
-  </si>
-  <si>
     <t>LP051754</t>
   </si>
   <si>
-    <t>LP050852</t>
-  </si>
-  <si>
     <t>LP051753</t>
   </si>
   <si>
-    <t>LP050851</t>
-  </si>
-  <si>
     <t>LP051752</t>
   </si>
   <si>
-    <t>LP050844</t>
-  </si>
-  <si>
     <t>LP051751</t>
   </si>
   <si>
-    <t>LP050842</t>
-  </si>
-  <si>
     <t>LP051750</t>
   </si>
   <si>
-    <t>LP050838</t>
-  </si>
-  <si>
     <t>LP051749</t>
   </si>
   <si>
-    <t>LP050831</t>
-  </si>
-  <si>
     <t>LP051746</t>
   </si>
   <si>
-    <t>LP050827</t>
-  </si>
-  <si>
     <t>LP051745</t>
   </si>
   <si>
-    <t>LP050826</t>
-  </si>
-  <si>
     <t>LP051736</t>
   </si>
   <si>
-    <t>LP050825</t>
-  </si>
-  <si>
     <t>LP051709</t>
   </si>
   <si>
-    <t>LP050795</t>
-  </si>
-  <si>
     <t>LP051687</t>
   </si>
   <si>
-    <t>LP050708</t>
-  </si>
-  <si>
     <t>LP051686</t>
   </si>
   <si>
-    <t>LP050701</t>
-  </si>
-  <si>
     <t>LP051685</t>
   </si>
   <si>
-    <t>LP050699</t>
-  </si>
-  <si>
     <t>LP051684</t>
   </si>
   <si>
-    <t>LP050698</t>
-  </si>
-  <si>
     <t>LP051683</t>
   </si>
   <si>
-    <t>LP050697</t>
-  </si>
-  <si>
     <t>LP051682</t>
   </si>
   <si>
-    <t>LP050696</t>
-  </si>
-  <si>
     <t>LP051680</t>
   </si>
   <si>
-    <t>LP050695</t>
-  </si>
-  <si>
     <t>LP051665</t>
   </si>
   <si>
-    <t>LP050694</t>
-  </si>
-  <si>
     <t>LP051664</t>
   </si>
   <si>
-    <t>LP050693</t>
-  </si>
-  <si>
     <t>LP051661</t>
   </si>
   <si>
-    <t>LP050692</t>
-  </si>
-  <si>
     <t>LP051659</t>
   </si>
   <si>
-    <t>LP050691</t>
-  </si>
-  <si>
     <t>LP051658</t>
   </si>
   <si>
-    <t>LP050636</t>
-  </si>
-  <si>
     <t>LP051657</t>
   </si>
   <si>
-    <t>LP050635</t>
-  </si>
-  <si>
     <t>LP051656</t>
   </si>
   <si>
-    <t>LP050633</t>
-  </si>
-  <si>
     <t>LP051629</t>
   </si>
   <si>
-    <t>LP050631</t>
-  </si>
-  <si>
     <t>LP051627</t>
   </si>
   <si>
-    <t>LP050610</t>
-  </si>
-  <si>
     <t>LP051626</t>
   </si>
   <si>
-    <t>LP050608</t>
-  </si>
-  <si>
     <t>LP051618</t>
-  </si>
-  <si>
-    <t>LP050607</t>
   </si>
   <si>
     <t>LP051617</t>
@@ -1024,897 +751,624 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:B122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="E3" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="E4" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="E5" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="E6" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="E7" t="s">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="E8" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="E9" t="s">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="E10" t="s">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="E11" t="s">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="E12" t="s">
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="E13" t="s">
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="E14" t="s">
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="E15" t="s">
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>31</v>
       </c>
-      <c r="E16" t="s">
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>33</v>
       </c>
-      <c r="E17" t="s">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>35</v>
       </c>
-      <c r="E18" t="s">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>37</v>
       </c>
-      <c r="E19" t="s">
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>39</v>
       </c>
-      <c r="E20" t="s">
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>41</v>
       </c>
-      <c r="E21" t="s">
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>43</v>
       </c>
-      <c r="E22" t="s">
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>45</v>
       </c>
-      <c r="E23" t="s">
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>47</v>
       </c>
-      <c r="E24" t="s">
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>49</v>
       </c>
-      <c r="E25" t="s">
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>51</v>
       </c>
-      <c r="E26" t="s">
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>53</v>
       </c>
-      <c r="E27" t="s">
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>55</v>
       </c>
-      <c r="E28" t="s">
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>57</v>
       </c>
-      <c r="E29" t="s">
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>59</v>
       </c>
-      <c r="E30" t="s">
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>61</v>
       </c>
-      <c r="E31" t="s">
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>63</v>
       </c>
-      <c r="E32" t="s">
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>65</v>
       </c>
-      <c r="E33" t="s">
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>67</v>
       </c>
-      <c r="E34" t="s">
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>69</v>
       </c>
-      <c r="E35" t="s">
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>71</v>
       </c>
-      <c r="E36" t="s">
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>73</v>
       </c>
-      <c r="E37" t="s">
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>75</v>
       </c>
-      <c r="E38" t="s">
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>77</v>
       </c>
-      <c r="E39" t="s">
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>79</v>
       </c>
-      <c r="E40" t="s">
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>81</v>
       </c>
-      <c r="E41" t="s">
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>83</v>
       </c>
-      <c r="E42" t="s">
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>85</v>
       </c>
-      <c r="E43" t="s">
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>87</v>
       </c>
-      <c r="E44" t="s">
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>89</v>
       </c>
-      <c r="E45" t="s">
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>91</v>
       </c>
-      <c r="E46" t="s">
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>93</v>
       </c>
-      <c r="E47" t="s">
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
         <v>95</v>
       </c>
-      <c r="E48" t="s">
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>97</v>
       </c>
-      <c r="E49" t="s">
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>99</v>
       </c>
-      <c r="E50" t="s">
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
         <v>101</v>
       </c>
-      <c r="E51" t="s">
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
         <v>103</v>
       </c>
-      <c r="E52" t="s">
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
         <v>105</v>
       </c>
-      <c r="E53" t="s">
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>107</v>
       </c>
-      <c r="E54" t="s">
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>109</v>
       </c>
-      <c r="E55" t="s">
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
         <v>111</v>
       </c>
-      <c r="E56" t="s">
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>113</v>
       </c>
-      <c r="E57" t="s">
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
         <v>115</v>
       </c>
-      <c r="E58" t="s">
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
         <v>117</v>
       </c>
-      <c r="E59" t="s">
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
         <v>119</v>
       </c>
-      <c r="E60" t="s">
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
         <v>121</v>
       </c>
-      <c r="E61" t="s">
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
         <v>122</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>123</v>
-      </c>
-      <c r="E62" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>125</v>
-      </c>
-      <c r="E63" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>127</v>
-      </c>
-      <c r="E64" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>129</v>
-      </c>
-      <c r="E65" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>131</v>
-      </c>
-      <c r="E66" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>133</v>
-      </c>
-      <c r="E67" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>135</v>
-      </c>
-      <c r="E68" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>137</v>
-      </c>
-      <c r="E69" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>139</v>
-      </c>
-      <c r="E70" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>141</v>
-      </c>
-      <c r="E71" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>143</v>
-      </c>
-      <c r="E72" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>145</v>
-      </c>
-      <c r="E73" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>147</v>
-      </c>
-      <c r="E74" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>149</v>
-      </c>
-      <c r="E75" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>151</v>
-      </c>
-      <c r="E76" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>153</v>
-      </c>
-      <c r="E77" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>155</v>
-      </c>
-      <c r="E78" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>157</v>
-      </c>
-      <c r="E79" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>159</v>
-      </c>
-      <c r="E80" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>161</v>
-      </c>
-      <c r="E81" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>163</v>
-      </c>
-      <c r="E82" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>165</v>
-      </c>
-      <c r="E83" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>167</v>
-      </c>
-      <c r="E84" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>169</v>
-      </c>
-      <c r="E85" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>171</v>
-      </c>
-      <c r="E86" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>173</v>
-      </c>
-      <c r="E87" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>175</v>
-      </c>
-      <c r="E88" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>177</v>
-      </c>
-      <c r="E89" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>179</v>
-      </c>
-      <c r="E90" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>181</v>
-      </c>
-      <c r="E91" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E92" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E93" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E94" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E95" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E96" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="97" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E97" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="98" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E98" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="99" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E99" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="100" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E100" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="101" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E101" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="102" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E102" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="103" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E103" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="104" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E104" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="105" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E105" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="106" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E106" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="107" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E107" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="108" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E108" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="109" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E109" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="110" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E110" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="111" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E111" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="112" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E112" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="113" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E113" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="114" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E114" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="115" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E115" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="116" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E116" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="117" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E117" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="118" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E118" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="119" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E119" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="120" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E120" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="121" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E121" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="122" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E122" t="s">
-        <v>213</v>
       </c>
     </row>
   </sheetData>
